--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MISSOURI_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MISSOURI_2022.xlsx
@@ -1201,7 +1201,7 @@
         <v>19</v>
       </c>
       <c r="D47">
-        <v>0.009519038076152305</v>
+        <v>0.009519038076152304</v>
       </c>
     </row>
     <row r="48">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C94">
@@ -3037,7 +3037,7 @@
         <v>18</v>
       </c>
       <c r="D149">
-        <v>0.009018036072144289</v>
+        <v>0.009018036072144287</v>
       </c>
     </row>
     <row r="150">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C151">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C155">
@@ -3577,7 +3577,7 @@
         <v>18</v>
       </c>
       <c r="D179">
-        <v>0.009018036072144289</v>
+        <v>0.009018036072144287</v>
       </c>
     </row>
     <row r="180">
@@ -3937,7 +3937,7 @@
         <v>18</v>
       </c>
       <c r="D199">
-        <v>0.009018036072144289</v>
+        <v>0.009018036072144287</v>
       </c>
     </row>
     <row r="200">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C357">
